--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-elicitation-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-elicitation-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Yêu cầu chức năng định nghĩa các hành vi, dịch vụ hoặc chức năng cụ thể mà hệ thống phần mềm phải thực hiện khi vận hành.</v>
       </c>
       <c r="F2" t="str">
+        <v>Các tiêu chuẩn về hiệu năng, bảo mật và tính khả dụng — quy định ràng buộc phi chức năng của hệ thống</v>
+      </c>
+      <c r="G2" t="str">
         <v>Những gì hệ thống phải thực hiện và cung cấp cho người dùng — quy định chức năng nghiệp vụ cụ thể</v>
       </c>
-      <c r="G2" t="str">
-        <v>Các tiêu chuẩn về hiệu năng, bảo mật và tính khả dụng — quy định ràng buộc phi chức năng của hệ thống</v>
-      </c>
       <c r="H2" t="str">
+        <v>Thời gian và ngân sách cần thiết để hoàn thành dự án — quy định các ràng buộc về mặt quản lý dự án</v>
+      </c>
+      <c r="I2" t="str">
         <v>Công nghệ và ngôn ngữ lập trình được sử dụng để phát triển — quy định giới hạn triển khai của dự án</v>
       </c>
-      <c r="I2" t="str">
-        <v>Thời gian và ngân sách cần thiết để hoàn thành dự án — quy định các ràng buộc về mặt quản lý dự án</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -495,16 +495,16 @@
         <v>Khả năng thanh toán qua thẻ tín dụng của cổng thanh toán điện tử — tính năng nghiệp vụ của hệ thống</v>
       </c>
       <c r="G3" t="str">
+        <v>Khả năng chịu tải và thời gian phản hồi của hệ thống dưới 2 giây — đặc tính vận hành và hiệu năng hệ thống</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Tính năng gửi email thông báo tự động cho khách hàng hằng ngày — hành vi xử lý dữ liệu của hệ thống</v>
+      </c>
+      <c r="I3" t="str">
         <v>Chức năng đăng nhập bằng vân tay của ứng dụng di động — tính năng bảo mật người dùng cụ thể</v>
       </c>
-      <c r="H3" t="str">
-        <v>Khả năng chịu tải và thời gian phản hồi của hệ thống dưới 2 giây — đặc tính vận hành và hiệu năng hệ thống</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Tính năng gửi email thông báo tự động cho khách hàng hằng ngày — hành vi xử lý dữ liệu của hệ thống</v>
-      </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Bảng câu hỏi khảo sát (Survey) là công cụ tối ưu để thu thập phản hồi nhanh chóng và định lượng từ số lượng lớn đối tượng.</v>
       </c>
       <c r="F4" t="str">
+        <v>Tạo bản mẫu (Prototyping) — thiết kế giao diện thử nghiệm để người dùng tương tác</v>
+      </c>
+      <c r="G4" t="str">
         <v>Phỏng vấn sâu (In-depth Interview) — tiếp cận từng cá nhân để lấy phản hồi chi tiết</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Bảng câu hỏi khảo sát (Survey/Questionnaire) — gửi câu hỏi định sẵn để thu thập dữ liệu định lượng lớn</v>
       </c>
       <c r="H4" t="str">
         <v>Quan sát trực tiếp (Observation) — theo dõi hành vi làm việc thực tế của người dùng</v>
       </c>
       <c r="I4" t="str">
-        <v>Tạo bản mẫu (Prototyping) — thiết kế giao diện thử nghiệm để người dùng tương tác</v>
+        <v>Bảng câu hỏi khảo sát (Survey/Questionnaire) — gửi câu hỏi định sẵn để thu thập dữ liệu định lượng lớn</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>User Story chuẩn có định dạng: "As a [role], I want [action], so that [benefit]" giúp tập trung vào đối tượng và giá trị thực tế mang lại.</v>
       </c>
       <c r="F5" t="str">
-        <v>Với tư cách là [vai trò], tôi muốn [chức năng], để [lợi ích] — định dạng chuẩn tập trung vào giá trị người dùng</v>
+        <v>Nếu [điều kiện] xảy ra thì [kết quả] phải hiển thị trên [giao diện] — định dạng rẽ nhánh điều kiện</v>
       </c>
       <c r="G5" t="str">
         <v>Hệ thống phải thực hiện [chức năng] cho [đối tượng] tại [thời điểm] — định dạng kỹ thuật hệ thống</v>
       </c>
       <c r="H5" t="str">
-        <v>Nếu [điều kiện] xảy ra thì [kết quả] phải hiển thị trên [giao diện] — định dạng rẽ nhánh điều kiện</v>
+        <v>Với tư cách là [vai trò], tôi muốn [chức năng], để [lợi ích] — định dạng chuẩn tập trung vào giá trị người dùng</v>
       </c>
       <c r="I5" t="str">
         <v>Nhà phát triển cần lập trình [tính năng] bằng cách sử dụng [công nghệ] — định dạng hướng triển khai kỹ thuật</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -620,19 +620,19 @@
         <v>MoSCoW viết tắt của Must have, Should have, Could have, và Won't have, là kỹ thuật phổ biến để sắp xếp độ ưu tiên yêu cầu.</v>
       </c>
       <c r="F7" t="str">
+        <v>Kiểm tra tính đúng đắn về mặt logic của các biểu đồ quy trình nghiệp vụ — xác thực luồng nghiệp vụ</v>
+      </c>
+      <c r="G7" t="str">
         <v>Sắp xếp thứ tự ưu tiên của các yêu cầu theo các mức độ quan trọng — phân loại Must, Should, Could, Won't</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Ước lượng độ phức tạp và kích thước của yêu cầu bằng điểm câu chuyện — đo lường Story Points</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Kiểm tra tính đúng đắn về mặt logic của các biểu đồ quy trình nghiệp vụ — xác thực luồng nghiệp vụ</v>
       </c>
       <c r="I7" t="str">
         <v>Theo dõi tiến độ phát triển của các tính năng trên bảng Kanban — quản lý trạng thái công việc</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,10 +652,10 @@
         <v>Ngôn ngữ Gherkin định nghĩa kịch bản kiểm thử bằng cách thiết lập bối cảnh (Given), hành động kích hoạt (When) và kết quả hiển thị (Then).</v>
       </c>
       <c r="F8" t="str">
+        <v>Start (Bắt đầu) - Process (Xử lý) - End (Kết thúc) — cấu trúc luồng tuần tự của thuật toán</v>
+      </c>
+      <c r="G8" t="str">
         <v>Given (Bối cảnh) - When (Hành động) - Then (Kết quả mong đợi) — cấu trúc chuẩn mô tả kịch bản hành vi</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Start (Bắt đầu) - Process (Xử lý) - End (Kết thúc) — cấu trúc luồng tuần tự của thuật toán</v>
       </c>
       <c r="H8" t="str">
         <v>Input (Đầu vào) - Output (Đầu ra) - Validate (Xác thực) — cấu trúc kiểm tra dữ liệu kỹ thuật</v>
@@ -664,7 +664,7 @@
         <v>If (Nếu) - Then (Thì) - Else (Ngược lại) — cấu trúc câu lệnh điều kiện lập trình</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -690,10 +690,10 @@
         <v>Product Owner (PO) — người đại diện cho khách hàng và quản lý giá trị sản phẩm</v>
       </c>
       <c r="H9" t="str">
+        <v>Tech Lead — người chịu trách nhiệm về kiến trúc kỹ thuật và phân chia task lập trình</v>
+      </c>
+      <c r="I9" t="str">
         <v>Business Analyst (BA) — người viết tài liệu đặc tả và phân tích nghiệp vụ chi tiết</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Tech Lead — người chịu trách nhiệm về kiến trúc kỹ thuật và phân chia task lập trình</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -716,19 +716,19 @@
         <v>Requirement Elicitation là quá trình khơi gợi, thu thập và làm rõ các yêu cầu ẩn từ phía khách hàng thông qua nhiều kỹ thuật.</v>
       </c>
       <c r="F10" t="str">
+        <v>Vẽ sơ đồ luồng dữ liệu của cơ sở dữ liệu quan hệ — thiết kế cấu trúc database</v>
+      </c>
+      <c r="G10" t="str">
         <v>Khơi gợi và khai thác yêu cầu từ phía khách hàng và các bên liên quan — tìm hiểu mong muốn thực tế</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Lập trình thử nghiệm giao diện để demo cho khách hàng duyệt — tạo mẫu sản phẩm</v>
       </c>
       <c r="H10" t="str">
         <v>Kiểm thử tính năng trên môi trường Staging trước khi bàn giao — bảo đảm chất lượng</v>
       </c>
       <c r="I10" t="str">
-        <v>Vẽ sơ đồ luồng dữ liệu của cơ sở dữ liệu quan hệ — thiết kế cấu trúc database</v>
+        <v>Lập trình thử nghiệm giao diện để demo cho khách hàng duyệt — tạo mẫu sản phẩm</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -754,10 +754,10 @@
         <v>Người dùng có thể xuất báo cáo doanh thu dưới dạng file PDF — chức năng xuất xuất dữ liệu cụ thể</v>
       </c>
       <c r="H11" t="str">
+        <v>Mật khẩu của người dùng phải được mã hóa bằng thuật toán SHA-256 — yêu cầu bảo mật dữ liệu</v>
+      </c>
+      <c r="I11" t="str">
         <v>Giao diện web phải hiển thị tốt trên cả thiết bị di động và máy tính — yêu cầu tính tương thích giao diện</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Mật khẩu của người dùng phải được mã hóa bằng thuật toán SHA-256 — yêu cầu bảo mật dữ liệu</v>
       </c>
       <c r="J11">
         <v>2</v>
